--- a/data/trans_dic/P34B01_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,52; 61,85</t>
+          <t>55,79; 61,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,29; 56,38</t>
+          <t>49,12; 56,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,36; 60,83</t>
+          <t>52,33; 60,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,78; 51,14</t>
+          <t>45,68; 51,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,11; 51,76</t>
+          <t>45,59; 52,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,98; 47,65</t>
+          <t>42,05; 47,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,92; 55,15</t>
+          <t>50,59; 54,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,91; 52,69</t>
+          <t>47,96; 52,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,11; 52,25</t>
+          <t>47,14; 51,73</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,22; 41,72</t>
+          <t>37,15; 41,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,01; 56,72</t>
+          <t>52,09; 56,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,67; 65,44</t>
+          <t>39,39; 65,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,0; 51,95</t>
+          <t>47,17; 51,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,73; 56,29</t>
+          <t>51,89; 56,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,15; 76,79</t>
+          <t>60,42; 75,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,31; 45,69</t>
+          <t>42,54; 45,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,51; 55,72</t>
+          <t>52,55; 55,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,67; 67,62</t>
+          <t>52,4; 67,91</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,34; 41,62</t>
+          <t>32,0; 41,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,3; 59,61</t>
+          <t>51,31; 60,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,0; 73,84</t>
+          <t>66,43; 73,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,93; 56,84</t>
+          <t>46,97; 56,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,94; 64,58</t>
+          <t>55,57; 63,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,62; 69,11</t>
+          <t>62,06; 69,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,03; 47,8</t>
+          <t>40,86; 47,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,95; 60,95</t>
+          <t>54,76; 60,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,62; 70,26</t>
+          <t>65,22; 70,5</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,76; 46,37</t>
+          <t>42,99; 46,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,35; 55,77</t>
+          <t>52,2; 55,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,32; 65,18</t>
+          <t>45,64; 65,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,54; 51,17</t>
+          <t>47,68; 51,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,63; 55,11</t>
+          <t>51,52; 55,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,53; 68,48</t>
+          <t>58,56; 69,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,77; 48,29</t>
+          <t>45,71; 48,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,56; 54,91</t>
+          <t>52,52; 54,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,9; 64,81</t>
+          <t>53,77; 64,53</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más</t>
+          <t>Población que camina durante más de 30 minutos, 3 veces por semana o más (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>539958; 601543</t>
+          <t>542603; 602663</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>371803; 425302</t>
+          <t>370571; 424819</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269214; 312747</t>
+          <t>269043; 309462</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>612479; 684127</t>
+          <t>611077; 684414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>448736; 514794</t>
+          <t>453417; 521113</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>314550; 357067</t>
+          <t>315081; 354396</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1176484; 1274196</t>
+          <t>1168924; 1269959</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>837936; 921531</t>
+          <t>838876; 922192</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>595261; 660135</t>
+          <t>595593; 653607</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>730905; 819272</t>
+          <t>729513; 820104</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1079986; 1177646</t>
+          <t>1081488; 1174206</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>880676; 1490242</t>
+          <t>897049; 1493598</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>825363; 912265</t>
+          <t>828208; 912249</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1028611; 1119145</t>
+          <t>1031654; 1120750</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1361916; 1710375</t>
+          <t>1345776; 1684872</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1574040; 1699570</t>
+          <t>1582545; 1702258</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2134543; 2264859</t>
+          <t>2135887; 2265326</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2282583; 3046013</t>
+          <t>2360467; 3059210</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>155595; 200254</t>
+          <t>153971; 201739</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>275084; 325988</t>
+          <t>280591; 329665</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>426800; 477438</t>
+          <t>429564; 476895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215229; 260663</t>
+          <t>215434; 260148</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>307200; 354646</t>
+          <t>305134; 350408</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>411383; 454041</t>
+          <t>407733; 453997</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>385637; 449210</t>
+          <t>384038; 449245</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>602288; 668049</t>
+          <t>600138; 666596</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>855444; 915904</t>
+          <t>850199; 919017</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1461342; 1584631</t>
+          <t>1469427; 1583404</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1768124; 1883542</t>
+          <t>1763013; 1882426</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1558296; 2241022</t>
+          <t>1569015; 2240795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1688932; 1817612</t>
+          <t>1693674; 1816321</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1823553; 1946667</t>
+          <t>1819823; 1948086</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2126605; 2488431</t>
+          <t>2127698; 2509240</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3189980; 3366123</t>
+          <t>3185938; 3360319</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3631479; 3793794</t>
+          <t>3628716; 3796292</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3811515; 4583372</t>
+          <t>3802397; 4563650</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B01_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P34B01_R-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,79; 61,97</t>
+          <t>55,52; 62,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,12; 56,32</t>
+          <t>49,06; 56,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,33; 60,19</t>
+          <t>51,74; 59,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,68; 51,16</t>
+          <t>45,6; 51,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,59; 52,39</t>
+          <t>45,5; 51,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,05; 47,29</t>
+          <t>42,77; 48,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,59; 54,97</t>
+          <t>50,55; 54,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,96; 52,73</t>
+          <t>48,02; 53,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,14; 51,73</t>
+          <t>47,38; 51,87</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,15; 41,76</t>
+          <t>37,11; 41,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,09; 56,55</t>
+          <t>52,01; 56,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,39; 65,59</t>
+          <t>64,14; 68,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,17; 51,95</t>
+          <t>46,78; 51,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,89; 56,37</t>
+          <t>51,9; 56,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,42; 75,65</t>
+          <t>65,62; 69,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,54; 45,76</t>
+          <t>42,36; 45,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,55; 55,73</t>
+          <t>52,33; 55,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,4; 67,91</t>
+          <t>65,31; 68,41</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,0; 41,93</t>
+          <t>32,56; 41,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,31; 60,28</t>
+          <t>51,27; 59,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,43; 73,75</t>
+          <t>66,88; 74,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,97; 56,72</t>
+          <t>47,27; 57,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,57; 63,81</t>
+          <t>55,53; 63,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,06; 69,1</t>
+          <t>63,06; 69,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,86; 47,8</t>
+          <t>40,91; 47,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,76; 60,82</t>
+          <t>54,65; 60,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,22; 70,5</t>
+          <t>65,93; 70,76</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,99; 46,33</t>
+          <t>42,88; 46,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,2; 55,73</t>
+          <t>52,46; 55,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,64; 65,18</t>
+          <t>63,59; 67,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,68; 51,13</t>
+          <t>47,75; 51,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,52; 55,15</t>
+          <t>51,76; 55,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,56; 69,06</t>
+          <t>60,9; 63,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,71; 48,21</t>
+          <t>45,71; 48,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,52; 54,94</t>
+          <t>52,44; 54,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,77; 64,53</t>
+          <t>62,68; 65,05</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290608</t>
+          <t>322206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>335543</t>
+          <t>371209</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>626151</t>
+          <t>693415</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>542603; 602663</t>
+          <t>540005; 604922</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>370571; 424819</t>
+          <t>370063; 424829</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269043; 309462</t>
+          <t>298790; 346202</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611077; 684414</t>
+          <t>610022; 684458</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>453417; 521113</t>
+          <t>452586; 511748</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>315081; 354396</t>
+          <t>349566; 393518</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1168924; 1269959</t>
+          <t>1167965; 1268436</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>838876; 922192</t>
+          <t>839793; 928236</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>595593; 653607</t>
+          <t>660867; 723510</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1313207</t>
+          <t>1469739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1495491</t>
+          <t>1458654</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2808698</t>
+          <t>2928393</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>729513; 820104</t>
+          <t>728887; 817423</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1081488; 1174206</t>
+          <t>1080018; 1173455</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>897049; 1493598</t>
+          <t>1421509; 1521793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>828208; 912249</t>
+          <t>821404; 908012</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1031654; 1120750</t>
+          <t>1031870; 1119198</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1345776; 1684872</t>
+          <t>1417695; 1497573</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1582545; 1702258</t>
+          <t>1575640; 1700213</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2135887; 2265326</t>
+          <t>2127169; 2261607</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2360467; 3059210</t>
+          <t>2858514; 2993901</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>454277</t>
+          <t>504239</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>431952</t>
+          <t>484554</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>886229</t>
+          <t>988793</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>153971; 201739</t>
+          <t>156672; 199638</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>280591; 329665</t>
+          <t>280376; 326245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>429564; 476895</t>
+          <t>475912; 528802</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215434; 260148</t>
+          <t>216778; 262405</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>305134; 350408</t>
+          <t>304957; 351215</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>407733; 453997</t>
+          <t>461130; 506707</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>384038; 449245</t>
+          <t>384476; 449657</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>600138; 666596</t>
+          <t>598934; 665236</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>850199; 919017</t>
+          <t>951257; 1020968</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2058091</t>
+          <t>2296183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2262987</t>
+          <t>2314416</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4321078</t>
+          <t>4610600</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1469427; 1583404</t>
+          <t>1465553; 1583582</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1763013; 1882426</t>
+          <t>1771807; 1886261</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1569015; 2240795</t>
+          <t>2229132; 2359096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1693674; 1816321</t>
+          <t>1696206; 1828003</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1819823; 1948086</t>
+          <t>1828217; 1947573</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2127698; 2509240</t>
+          <t>2258952; 2364738</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3185938; 3360319</t>
+          <t>3186251; 3362699</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3628716; 3796292</t>
+          <t>3623799; 3794044</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3802397; 4563650</t>
+          <t>4521992; 4693181</t>
         </is>
       </c>
     </row>
